--- a/backend/data/financials_by_company/002540.SZ.xlsx
+++ b/backend/data/financials_by_company/002540.SZ.xlsx
@@ -4166,197 +4166,197 @@
       </c>
       <c r="DN1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EZ1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="FA1" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Jiangsu Asia-Pacific Light Alloy Technology Co., Ltd. engages in the research and development, production, sale, and service of aluminum products in China and internationally. The company offers precision aluminum tubes, special profiles and high-precision bars, and other automotive and industrial aluminum extrusion extrusions. Its produsts are used in aerospace, military-civilian integration, air conditioning, and marine industries. The company was formerly known as Jiangsu Yatal Aluminium Co., Ltd. and changed its name to Jiangsu Asia-Pacific Light Alloy Technology Co., Ltd. in September 2007. Jiangsu Asia-Pacific Light Alloy Technology Co., Ltd. was founded in 2001 and is based in Wuxi, China.</t>
+          <t>Jiangsu Asia-Pacific Light Alloy Technology Co., Ltd. engages in the research and development, production, sale, and service of aluminum products in China and internationally. The company offers precision aluminum tubes, special profiles and high-precision bars, other automotive and industrial aluminum extrusions, and new energy vehicle components. Its produsts are used in aerospace, military, civilian integration, fusion, air conditioning, and marine engineering. The company was formerly known as Jiangsu Yatal Aluminium Co., Ltd. and changed its name to Jiangsu Asia-Pacific Light Alloy Technology Co., Ltd. in September 2007. Jiangsu Asia-Pacific Light Alloy Technology Co., Ltd. was founded in 2001 and is based in Wuxi, China.</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4458,76 +4458,76 @@
         <v>86400</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>5.08</v>
+        <v>4.82</v>
       </c>
       <c r="V2" t="n">
-        <v>5.04</v>
+        <v>4.83</v>
       </c>
       <c r="W2" t="n">
-        <v>4.92</v>
+        <v>4.82</v>
       </c>
       <c r="X2" t="n">
-        <v>5.09</v>
+        <v>4.95</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.08</v>
+        <v>4.82</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.04</v>
+        <v>4.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.92</v>
+        <v>4.82</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.09</v>
+        <v>4.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.91</v>
+        <v>3.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>1758585600</v>
+        <v>1783296000</v>
       </c>
       <c r="AF2" t="n">
         <v>1.0646</v>
       </c>
       <c r="AG2" t="n">
-        <v>4.82</v>
+        <v>4.85</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.219</v>
+        <v>0.238</v>
       </c>
       <c r="AI2" t="n">
-        <v>18.142857</v>
+        <v>17.535713</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10.367347</v>
+        <v>10.020408</v>
       </c>
       <c r="AK2" t="n">
-        <v>13327871</v>
+        <v>12224350</v>
       </c>
       <c r="AL2" t="n">
-        <v>13327871</v>
+        <v>12224350</v>
       </c>
       <c r="AM2" t="n">
-        <v>11649442</v>
+        <v>11144877</v>
       </c>
       <c r="AN2" t="n">
-        <v>9574791</v>
+        <v>11350371</v>
       </c>
       <c r="AO2" t="n">
-        <v>9574791</v>
+        <v>11350371</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.07</v>
+        <v>4.91</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.08</v>
+        <v>4.92</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -4536,13 +4536,13 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>6355811328</v>
+        <v>6143117312</v>
       </c>
       <c r="AU2" t="n">
-        <v>6355810874</v>
+        <v>6005491497</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.92</v>
+        <v>4.61</v>
       </c>
       <c r="AW2" t="n">
         <v>8.08</v>
@@ -4554,19 +4554,19 @@
         <v>2.092</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.7352484</v>
+        <v>0.71064365</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.8496</v>
+        <v>5.508</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.6821</v>
+        <v>6.60185</v>
       </c>
       <c r="BC2" t="n">
         <v>0.18</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.035433073</v>
+        <v>0.0373444</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -4577,31 +4577,31 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>7281687040</v>
+        <v>7071685120</v>
       </c>
       <c r="BH2" t="n">
         <v>0.042969998</v>
       </c>
       <c r="BI2" t="n">
-        <v>600148782</v>
+        <v>600099370</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1251143873</v>
+        <v>1251144062</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.54517</v>
+        <v>0.53967</v>
       </c>
       <c r="BL2" t="n">
         <v>0.05641</v>
       </c>
       <c r="BM2" t="n">
-        <v>1251143873</v>
+        <v>1251144062</v>
       </c>
       <c r="BN2" t="n">
         <v>4.592</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.1062717</v>
+        <v>1.0692508</v>
       </c>
       <c r="BP2" t="n">
         <v>1767139200</v>
@@ -4633,22 +4633,22 @@
         <v>1428883200</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.842</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="BZ2" t="n">
-        <v>11.123</v>
+        <v>10.802</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0.08960575</v>
+        <v>-0.17324185</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="CD2" t="n">
-        <v>1758585600</v>
+        <v>1783296000</v>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="CF2" t="n">
-        <v>5.08</v>
+        <v>4.91</v>
       </c>
       <c r="CG2" t="n">
         <v>7</v>
@@ -4773,146 +4773,146 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="DN2" t="b">
+        <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>1782111882</v>
-      </c>
-      <c r="DP2" t="inlineStr">
+        <v>1295314200000</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0.089999676</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>4.82 - 4.95</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>11144877</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.2999997</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.06507586</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>4.61 - 8.08</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.39232674</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-17.324184</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1651143540</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1651233600</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>11.97561</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.59800005</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-0.10856936</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-1.6918502</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.2562691</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>JIANGSU ASIA-PACIFIC LIGHT ALLO</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>Jiangsu Asia-Pacific Light Alloy Technology Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>[{'header': 'Dividend', 'message': '002540.SZ announced a cash dividend of CNY 0.08 with an ex-date of Jul. 6, 2026', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1783267200000, 'amount': '0.08'}}]</t>
+        </is>
+      </c>
+      <c r="EQ2" t="n">
+        <v>1783062240</v>
+      </c>
+      <c r="ER2" t="inlineStr">
         <is>
           <t>SHZ</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="ES2" t="inlineStr">
         <is>
           <t>finmb_75334081</t>
         </is>
       </c>
-      <c r="DR2" t="inlineStr">
+      <c r="ET2" t="inlineStr">
         <is>
           <t>Asia/Shanghai</t>
         </is>
       </c>
-      <c r="DS2" t="inlineStr">
+      <c r="EU2" t="inlineStr">
         <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="DT2" t="n">
+      <c r="EV2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DU2" t="inlineStr">
+      <c r="EW2" t="inlineStr">
         <is>
           <t>cn_market</t>
         </is>
       </c>
-      <c r="DV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1295314200000</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>4.92 - 5.09</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>11649442</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.15999985</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.032520294</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>4.92 - 8.08</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.37128714</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-8.960575</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1651143540</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1651233600</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>12.390244</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>-0.7695999</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>-0.13156454</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>-1.6020999</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>-0.23975995</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EY2" t="inlineStr">
-        <is>
-          <t>JIANGSU ASIA-PACIFIC LIGHT ALLO</t>
-        </is>
-      </c>
-      <c r="EZ2" t="inlineStr">
-        <is>
-          <t>Jiangsu Asia-Pacific Light Alloy Technology Co., Ltd.</t>
-        </is>
+      <c r="EX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>1.8672131</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>4.91</v>
       </c>
       <c r="FA2" t="inlineStr"/>
     </row>
